--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -54,15 +54,6 @@
     <t>交易平台</t>
   </si>
   <si>
-    <t>券面总额</t>
-  </si>
-  <si>
-    <t>本方券券面总额</t>
-  </si>
-  <si>
-    <t>融入券券面总额</t>
-  </si>
-  <si>
     <t>币种</t>
   </si>
   <si>
@@ -91,6 +82,18 @@
   </si>
   <si>
     <t>合作资产</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>券面总额/万元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本方券券面总额/万元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>融入券券面总额/万元</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -98,6 +101,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -142,9 +148,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -452,7 +459,9 @@
   <dimension ref="A1:X1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="23" width="15.625" customWidth="1"/>
+    <col min="1" max="12" width="15.625" customWidth="1"/>
+    <col min="13" max="15" width="15.625" style="2" customWidth="1"/>
+    <col min="16" max="23" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.15">
@@ -478,7 +487,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
@@ -492,45 +501,46 @@
       <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
         <v>19</v>
-      </c>
-      <c r="V1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>有效状态</t>
   </si>
@@ -79,10 +79,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>合作资产</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>券面总额/万元</t>
@@ -456,15 +452,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="12" width="15.625" customWidth="1"/>
-    <col min="13" max="15" width="15.625" style="2" customWidth="1"/>
-    <col min="16" max="23" width="15.625" customWidth="1"/>
+    <col min="1" max="11" width="15.625" customWidth="1"/>
+    <col min="12" max="14" width="15.625" style="2" customWidth="1"/>
+    <col min="15" max="22" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,20 +482,20 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>21</v>
@@ -507,34 +503,31 @@
       <c r="N1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>23</v>
+      <c r="O1" t="s">
+        <v>11</v>
       </c>
       <c r="P1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W1" t="s">
-        <v>18</v>
-      </c>
-      <c r="X1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpaceZhu\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>有效状态</t>
   </si>
@@ -33,15 +33,9 @@
     <t>组合代码</t>
   </si>
   <si>
-    <t>组合名称</t>
-  </si>
-  <si>
     <t>资产代码</t>
   </si>
   <si>
-    <t>资产名称</t>
-  </si>
-  <si>
     <t>交易方向</t>
   </si>
   <si>
@@ -91,6 +85,10 @@
   </si>
   <si>
     <t>合作资产</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产简称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -449,13 +447,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="23" width="15.625" customWidth="1"/>
+    <col min="1" max="22" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -472,61 +470,58 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
-      </c>
-      <c r="W1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpaceZhu\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workSpaceGZ\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>有效状态</t>
   </si>
@@ -72,13 +72,7 @@
     <t>交割日期</t>
   </si>
   <si>
-    <t>成交编号</t>
-  </si>
-  <si>
     <t>处理状态</t>
-  </si>
-  <si>
-    <t>资产推荐方</t>
   </si>
   <si>
     <t>备注</t>
@@ -89,6 +83,10 @@
   </si>
   <si>
     <t>资产简称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>银行间成交编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -447,13 +445,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="22" width="15.6328125" customWidth="1"/>
+    <col min="1" max="21" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,10 +468,10 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
@@ -515,13 +513,10 @@
         <v>17</v>
       </c>
       <c r="U1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" t="s">
         <v>18</v>
-      </c>
-      <c r="V1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workSpaceGZ\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workSpaceGZNEW\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -48,15 +48,6 @@
     <t>交易平台</t>
   </si>
   <si>
-    <t>券面总额</t>
-  </si>
-  <si>
-    <t>本方券券面总额</t>
-  </si>
-  <si>
-    <t>融入券券面总额</t>
-  </si>
-  <si>
     <t>币种</t>
   </si>
   <si>
@@ -87,6 +78,18 @@
   </si>
   <si>
     <t>银行间成交编号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>券面总额（万元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本方券券面总额（万元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>融入券券面总额（万元）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -448,7 +451,9 @@
   <dimension ref="A1:V1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="21" width="15.6328125" customWidth="1"/>
+    <col min="1" max="12" width="15.6328125" customWidth="1"/>
+    <col min="13" max="14" width="24.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="21" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -468,10 +473,10 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
@@ -485,38 +490,38 @@
       <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" t="s">
         <v>15</v>
-      </c>
-      <c r="S1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>有效状态</t>
   </si>
@@ -67,10 +67,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>合作资产</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>资产简称</t>
@@ -448,15 +444,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="12" width="15.6328125" customWidth="1"/>
-    <col min="13" max="14" width="24.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="21" width="15.6328125" customWidth="1"/>
+    <col min="1" max="11" width="15.6328125" customWidth="1"/>
+    <col min="12" max="13" width="24.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="20" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,22 +469,22 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
         <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>19</v>
@@ -496,31 +492,28 @@
       <c r="M1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>21</v>
+      <c r="N1" t="s">
+        <v>9</v>
       </c>
       <c r="O1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U1" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" t="s">
         <v>15</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
@@ -27,9 +27,6 @@
     <t>业务编号</t>
   </si>
   <si>
-    <t>委托代码</t>
-  </si>
-  <si>
     <t>组合代码</t>
   </si>
   <si>
@@ -86,6 +83,10 @@
   </si>
   <si>
     <t>融入券券面总额（万元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -459,62 +460,62 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>14</v>
-      </c>
-      <c r="T1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdBondInvestTrade001.xlsx
@@ -86,7 +86,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>指令编号</t>
+    <t>指令代码</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
